--- a/data/2024/counties_2024.xlsx
+++ b/data/2024/counties_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naughtm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581339B8-BF83-45A9-B9A2-AD8FEBA7BD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2545042D-D4DD-4E80-B598-EE08FF6A91DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{EC1684B5-88F2-42EA-A614-90B4A0278099}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC1684B5-88F2-42EA-A614-90B4A0278099}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Issued</t>
   </si>
@@ -44,12 +44,6 @@
     <t>Refused</t>
   </si>
   <si>
-    <t>Withdrawn</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
     <t>Carlow</t>
   </si>
   <si>
@@ -132,6 +126,9 @@
   </si>
   <si>
     <t>No County Entered</t>
+  </si>
+  <si>
+    <t>County</t>
   </si>
 </sst>
 </file>
@@ -209,17 +206,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -562,427 +553,329 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7B1D68-62A9-4A40-9CCF-9EDA7A1486C7}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4">
+        <v>70</v>
+      </c>
+      <c r="C2" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="4">
+        <v>233</v>
+      </c>
+      <c r="C3" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
-        <v>39390</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2456</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="B4" s="4">
+        <v>573</v>
+      </c>
+      <c r="C4" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>657</v>
+      </c>
+      <c r="C5" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3293</v>
+      </c>
+      <c r="C6" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>428</v>
+      </c>
+      <c r="C7" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>19141</v>
+      </c>
+      <c r="C8" s="4">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1269</v>
+      </c>
+      <c r="C10" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>542</v>
+      </c>
+      <c r="C11" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2342</v>
+      </c>
+      <c r="C12" s="4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>433</v>
+      </c>
+      <c r="C13" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>193</v>
+      </c>
+      <c r="C14" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>67</v>
+      </c>
+      <c r="C15" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1905</v>
+      </c>
+      <c r="C16" s="4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>147</v>
+      </c>
+      <c r="C17" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <v>804</v>
+      </c>
+      <c r="C18" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>504</v>
+      </c>
+      <c r="C19" s="4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1511</v>
+      </c>
+      <c r="C20" s="4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
+        <v>541</v>
+      </c>
+      <c r="C21" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4">
+        <v>484</v>
+      </c>
+      <c r="C22" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
+        <v>255</v>
+      </c>
+      <c r="C23" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <v>244</v>
+      </c>
+      <c r="C24" s="4">
         <v>31</v>
       </c>
-      <c r="B3" s="6">
-        <v>70</v>
-      </c>
-      <c r="C3" s="6">
-        <v>11</v>
-      </c>
-      <c r="D3" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6">
-        <v>233</v>
-      </c>
-      <c r="C4" s="6">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>703</v>
+      </c>
+      <c r="C25" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1297</v>
+      </c>
+      <c r="C26" s="4">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4">
+        <v>514</v>
+      </c>
+      <c r="C27" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="6">
-        <v>573</v>
-      </c>
-      <c r="C5" s="6">
-        <v>27</v>
-      </c>
-      <c r="D5" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="6">
-        <v>657</v>
-      </c>
-      <c r="C6" s="6">
-        <v>63</v>
-      </c>
-      <c r="D6" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6">
-        <v>3293</v>
-      </c>
-      <c r="C7" s="6">
-        <v>195</v>
-      </c>
-      <c r="D7" s="6">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="6">
-        <v>428</v>
-      </c>
-      <c r="C8" s="6">
-        <v>27</v>
-      </c>
-      <c r="D8" s="6">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>19141</v>
-      </c>
-      <c r="C9" s="6">
-        <v>967</v>
-      </c>
-      <c r="D9" s="6">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="6">
-        <v>1269</v>
-      </c>
-      <c r="C11" s="6">
-        <v>85</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="B28" s="4">
+        <v>868</v>
+      </c>
+      <c r="C28" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4">
+        <v>372</v>
+      </c>
+      <c r="C29" s="4">
         <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="6">
-        <v>542</v>
-      </c>
-      <c r="C12" s="6">
-        <v>29</v>
-      </c>
-      <c r="D12" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="6">
-        <v>2342</v>
-      </c>
-      <c r="C13" s="6">
-        <v>122</v>
-      </c>
-      <c r="D13" s="6">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="6">
-        <v>433</v>
-      </c>
-      <c r="C14" s="6">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="6">
-        <v>193</v>
-      </c>
-      <c r="C15" s="6">
-        <v>14</v>
-      </c>
-      <c r="D15" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="6">
-        <v>67</v>
-      </c>
-      <c r="C16" s="6">
-        <v>8</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="6">
-        <v>1905</v>
-      </c>
-      <c r="C17" s="6">
-        <v>86</v>
-      </c>
-      <c r="D17" s="6">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="6">
-        <v>147</v>
-      </c>
-      <c r="C18" s="6">
-        <v>17</v>
-      </c>
-      <c r="D18" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="6">
-        <v>804</v>
-      </c>
-      <c r="C19" s="6">
-        <v>33</v>
-      </c>
-      <c r="D19" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="6">
-        <v>504</v>
-      </c>
-      <c r="C20" s="6">
-        <v>36</v>
-      </c>
-      <c r="D20" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1511</v>
-      </c>
-      <c r="C21" s="6">
-        <v>111</v>
-      </c>
-      <c r="D21" s="6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="6">
-        <v>541</v>
-      </c>
-      <c r="C22" s="6">
-        <v>20</v>
-      </c>
-      <c r="D22" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="6">
-        <v>484</v>
-      </c>
-      <c r="C23" s="6">
-        <v>22</v>
-      </c>
-      <c r="D23" s="6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6">
-        <v>255</v>
-      </c>
-      <c r="C24" s="6">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6">
-        <v>244</v>
-      </c>
-      <c r="C25" s="6">
-        <v>31</v>
-      </c>
-      <c r="D25" s="6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6">
-        <v>703</v>
-      </c>
-      <c r="C26" s="6">
-        <v>45</v>
-      </c>
-      <c r="D26" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="6">
-        <v>1297</v>
-      </c>
-      <c r="C27" s="6">
-        <v>298</v>
-      </c>
-      <c r="D27" s="6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="6">
-        <v>514</v>
-      </c>
-      <c r="C28" s="6">
-        <v>40</v>
-      </c>
-      <c r="D28" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6">
-        <v>868</v>
-      </c>
-      <c r="C29" s="6">
-        <v>75</v>
-      </c>
-      <c r="D29" s="6">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6">
-        <v>372</v>
-      </c>
-      <c r="C30" s="6">
-        <v>25</v>
-      </c>
-      <c r="D30" s="6">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -991,6 +884,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
@@ -1027,15 +929,6 @@
     </mbbd3fafa5ab4e5eb8a6a5e099cef439>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1248,6 +1141,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCCD1B9A-8977-4A9D-A2AE-30E55D48FFBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D2653AC-5E95-4D0D-A371-0CA2CF7C25C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1259,14 +1160,6 @@
     <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCCD1B9A-8977-4A9D-A2AE-30E55D48FFBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
